--- a/Analysis/clean data/Survey 1_scored_near complete_16.6.26.xlsx
+++ b/Analysis/clean data/Survey 1_scored_near complete_16.6.26.xlsx
@@ -13999,12 +13999,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Multi-country: Australia &amp;New Zealand</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ZC &amp; HK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
